--- a/course-schedule.xlsx
+++ b/course-schedule.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="109">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -1982,13 +1982,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Final Part 1</t>
+    <t xml:space="preserve">Final Exam Review</t>
   </si>
   <si>
     <t xml:space="preserve">Everything!</t>
   </si>
   <si>
+    <t xml:space="preserve">- [ ] [Final Exam Review](exams/final/exam-questions.qmd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- [ ] Final Exam on Canvas -- Due Dec 17, 12pm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Final Exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final exam will be completed online based on class consensus.</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
@@ -2664,9 +2673,15 @@
         <v>86</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2676,12 +2691,14 @@
         <v>46008</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2704,16 +2721,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2721,13 +2738,13 @@
         <v>20251023</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2735,13 +2752,13 @@
         <v>20251217</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2784,21 +2801,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>20250825</v>
@@ -2809,7 +2826,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>20250901</v>
@@ -2817,7 +2834,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>20251020</v>
@@ -2828,7 +2845,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>20251126</v>
@@ -2839,7 +2856,7 @@
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>20251215</v>
@@ -2850,10 +2867,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
